--- a/heartowiki.xlsx
+++ b/heartowiki.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="566">
   <si>
     <t>도감 버전</t>
   </si>
@@ -1534,10 +1534,7 @@
     <t>잔디케이크</t>
   </si>
   <si>
-    <t>획득불가</t>
-  </si>
-  <si>
-    <t>쌀가루 ×1
+    <t>밀 ×1
 우유 ×1
 말차가루 ×1
 잡초 ×1</t>
@@ -1546,10 +1543,7 @@
     <t>잔디케이크 레시피</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>중국 서버 한정 7일 출석 보상. 글로벌 서버에서는 도감에만 있을 뿐 제작이 불가능함.</t>
+    <t>웨슬리와 울피 인연 소집령 6일차 출석 보상</t>
   </si>
   <si>
     <t>얼음컵 커피</t>
@@ -13910,660 +13904,660 @@
       <c r="A57" s="26" t="s">
         <v>480</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="27">
+        <v>1.0</v>
+      </c>
+      <c r="C57" s="27" t="s">
         <v>481</v>
       </c>
-      <c r="C57" s="26" t="s">
+      <c r="D57" s="26" t="s">
         <v>482</v>
       </c>
-      <c r="D57" s="26" t="s">
+      <c r="E57" s="27">
+        <v>690.0</v>
+      </c>
+      <c r="F57" s="27" t="s">
         <v>483</v>
-      </c>
-      <c r="E57" s="27" t="s">
-        <v>484</v>
-      </c>
-      <c r="F57" s="27" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="26" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B58" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E58" s="27">
         <v>280.0</v>
       </c>
       <c r="F58" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="26" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B59" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E59" s="27">
         <v>280.0</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="26" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B60" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E60" s="27">
         <v>630.0</v>
       </c>
       <c r="F60" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="26" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B61" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E61" s="27">
         <v>340.0</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="26" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B62" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E62" s="27">
         <v>330.0</v>
       </c>
       <c r="F62" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="26" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B63" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E63" s="27">
         <v>330.0</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="26" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B64" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E64" s="27">
         <v>350.0</v>
       </c>
       <c r="F64" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="26" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B65" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E65" s="27">
         <v>360.0</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="26" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B66" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E66" s="27">
         <v>360.0</v>
       </c>
       <c r="F66" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="26" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B67" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E67" s="27">
         <v>1630.0</v>
       </c>
       <c r="F67" s="27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="26" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B68" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E68" s="27">
         <v>130.0</v>
       </c>
       <c r="F68" s="27" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E69" s="12">
         <v>900.0</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C70" s="27" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E70" s="12">
         <v>820.0</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C71" s="27" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E71" s="12">
         <v>280.0</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C72" s="27" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E72" s="12">
         <v>1230.0</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C73" s="27" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E73" s="12">
         <v>1150.0</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C74" s="27" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E74" s="12">
         <v>260.0</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C75" s="27" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E75" s="12">
         <v>330.0</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C76" s="27" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E76" s="12">
         <v>330.0</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C77" s="27" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E77" s="12">
         <v>330.0</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C78" s="27" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E78" s="12">
         <v>330.0</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C79" s="27" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E79" s="12">
         <v>330.0</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C80" s="27" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E80" s="12">
         <v>460.0</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C81" s="27" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E81" s="12">
         <v>480.0</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C82" s="27" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E82" s="12">
         <v>480.0</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C83" s="27" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E83" s="12">
         <v>480.0</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C84" s="27" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E84" s="12">
         <v>480.0</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E85" s="12">
         <v>800.0</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C86" s="27" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E86" s="12">
         <v>910.0</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C87" s="27" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E87" s="12">
         <v>480.0</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C88" s="27" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E88" s="12">
         <v>1960.0</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C89" s="27" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E89" s="12">
         <v>2370.0</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/heartowiki.xlsx
+++ b/heartowiki.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="577">
   <si>
     <t>도감 버전</t>
   </si>
@@ -500,6 +500,12 @@
     <t>갈색 감독 참문어</t>
   </si>
   <si>
+    <t>꽃무늬 감독 참문어</t>
+  </si>
+  <si>
+    <t>문어 엔터테인먼트</t>
+  </si>
+  <si>
     <t>세부위치</t>
   </si>
   <si>
@@ -794,9 +800,6 @@
     <t>겨울 옷 청둥오리</t>
   </si>
   <si>
-    <t>상시</t>
-  </si>
-  <si>
     <t>겨울 옷 홍머리오리</t>
   </si>
   <si>
@@ -809,6 +812,27 @@
     <t>근교 호숫가</t>
   </si>
   <si>
+    <t>신사 초록 비둘기</t>
+  </si>
+  <si>
+    <t>신사 파랑 비둘기</t>
+  </si>
+  <si>
+    <t>영혼의 참나무 숲</t>
+  </si>
+  <si>
+    <t>신사 회색 비둘기</t>
+  </si>
+  <si>
+    <t>신사 빨강 비둘기</t>
+  </si>
+  <si>
+    <t>신사 무늬 비둘기</t>
+  </si>
+  <si>
+    <t>배우 비둘기 사건</t>
+  </si>
+  <si>
     <t>호랑나비</t>
   </si>
   <si>
@@ -1034,6 +1058,9 @@
     <t>얼음 결정 멜포메네길쭉나비</t>
   </si>
   <si>
+    <t>얼음결정 나비사건</t>
+  </si>
+  <si>
     <t>스크립터 분홍 호박벌</t>
   </si>
   <si>
@@ -1044,6 +1071,12 @@
   </si>
   <si>
     <t>스크립터 보라 호박벌</t>
+  </si>
+  <si>
+    <t>스크립터 금색 호박벌</t>
+  </si>
+  <si>
+    <t>스크립터 벌 사건</t>
   </si>
   <si>
     <t>재료</t>
@@ -4886,7 +4919,28 @@
       <c r="H107" s="13"/>
     </row>
     <row r="108">
-      <c r="F108" s="14"/>
+      <c r="A108" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D108" s="13"/>
+      <c r="E108" s="12">
+        <v>320.0</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="109">
       <c r="F109" s="14"/>
@@ -7591,7 +7645,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>8</v>
@@ -7602,13 +7656,13 @@
     </row>
     <row r="2">
       <c r="A2" s="12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B2" s="12">
         <v>1.0</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="12" t="s">
@@ -7620,13 +7674,13 @@
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B3" s="12">
         <v>1.0</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="12" t="s">
@@ -7638,13 +7692,13 @@
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B4" s="12">
         <v>1.0</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D4" s="13"/>
       <c r="E4" s="12" t="s">
@@ -7656,13 +7710,13 @@
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B5" s="12">
         <v>1.0</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="12" t="s">
@@ -7674,13 +7728,13 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B6" s="12">
         <v>1.0</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="12" t="s">
@@ -7692,13 +7746,13 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B7" s="12">
         <v>1.0</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="12" t="s">
@@ -7710,13 +7764,13 @@
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B8" s="12">
         <v>1.0</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="12" t="s">
@@ -7728,13 +7782,13 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B9" s="12">
         <v>1.0</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="12" t="s">
@@ -7746,13 +7800,13 @@
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B10" s="12">
         <v>1.0</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="12" t="s">
@@ -7764,13 +7818,13 @@
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B11" s="12">
         <v>1.0</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="12" t="s">
@@ -7782,13 +7836,13 @@
     </row>
     <row r="12">
       <c r="A12" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B12" s="12">
         <v>1.0</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="12" t="s">
@@ -7800,7 +7854,7 @@
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B13" s="12">
         <v>1.0</v>
@@ -7818,13 +7872,13 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B14" s="12">
         <v>1.0</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="12" t="s">
@@ -7836,13 +7890,13 @@
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B15" s="12">
         <v>2.0</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="12" t="s">
@@ -7854,13 +7908,13 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B16" s="12">
         <v>2.0</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="12" t="s">
@@ -7872,13 +7926,13 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B17" s="12">
         <v>2.0</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="12" t="s">
@@ -7890,13 +7944,13 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B18" s="12">
         <v>2.0</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="12" t="s">
@@ -7908,13 +7962,13 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B19" s="12">
         <v>2.0</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="12" t="s">
@@ -7926,7 +7980,7 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B20" s="12">
         <v>2.0</v>
@@ -7944,13 +7998,13 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B21" s="12">
         <v>2.0</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="12" t="s">
@@ -7962,13 +8016,13 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B22" s="12">
         <v>3.0</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="12" t="s">
@@ -7980,16 +8034,16 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B23" s="12">
         <v>3.0</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>14</v>
@@ -8000,16 +8054,16 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B24" s="12">
         <v>3.0</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>14</v>
@@ -8020,13 +8074,13 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B25" s="12">
         <v>3.0</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="12" t="s">
@@ -8038,7 +8092,7 @@
     </row>
     <row r="26">
       <c r="A26" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B26" s="12">
         <v>3.0</v>
@@ -8056,7 +8110,7 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B27" s="12">
         <v>3.0</v>
@@ -8074,13 +8128,13 @@
     </row>
     <row r="28">
       <c r="A28" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B28" s="12">
         <v>3.0</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="12" t="s">
@@ -8092,7 +8146,7 @@
     </row>
     <row r="29">
       <c r="A29" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B29" s="12">
         <v>3.0</v>
@@ -8110,16 +8164,16 @@
     </row>
     <row r="30">
       <c r="A30" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B30" s="12">
         <v>4.0</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>14</v>
@@ -8130,16 +8184,16 @@
     </row>
     <row r="31">
       <c r="A31" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B31" s="12">
         <v>4.0</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>14</v>
@@ -8150,16 +8204,16 @@
     </row>
     <row r="32">
       <c r="A32" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B32" s="12">
         <v>4.0</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>14</v>
@@ -8170,16 +8224,16 @@
     </row>
     <row r="33">
       <c r="A33" s="12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B33" s="12">
         <v>4.0</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>14</v>
@@ -8190,16 +8244,16 @@
     </row>
     <row r="34">
       <c r="A34" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B34" s="12">
         <v>4.0</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>14</v>
@@ -8210,16 +8264,16 @@
     </row>
     <row r="35">
       <c r="A35" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B35" s="12">
         <v>4.0</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>14</v>
@@ -8230,13 +8284,13 @@
     </row>
     <row r="36">
       <c r="A36" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B36" s="12">
         <v>4.0</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>17</v>
@@ -8250,16 +8304,16 @@
     </row>
     <row r="37">
       <c r="A37" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B37" s="12">
         <v>5.0</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>14</v>
@@ -8270,16 +8324,16 @@
     </row>
     <row r="38">
       <c r="A38" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B38" s="12">
         <v>5.0</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>14</v>
@@ -8290,13 +8344,13 @@
     </row>
     <row r="39">
       <c r="A39" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B39" s="12">
         <v>5.0</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="12" t="s">
@@ -8308,16 +8362,16 @@
     </row>
     <row r="40">
       <c r="A40" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B40" s="12">
         <v>5.0</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>14</v>
@@ -8328,16 +8382,16 @@
     </row>
     <row r="41">
       <c r="A41" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B41" s="12">
         <v>5.0</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>14</v>
@@ -8348,7 +8402,7 @@
     </row>
     <row r="42">
       <c r="A42" s="12" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B42" s="12">
         <v>5.0</v>
@@ -8357,7 +8411,7 @@
         <v>53</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>14</v>
@@ -8368,16 +8422,16 @@
     </row>
     <row r="43">
       <c r="A43" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B43" s="12">
         <v>6.0</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>14</v>
@@ -8388,16 +8442,16 @@
     </row>
     <row r="44">
       <c r="A44" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B44" s="12">
         <v>6.0</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>14</v>
@@ -8408,13 +8462,13 @@
     </row>
     <row r="45">
       <c r="A45" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B45" s="12">
         <v>6.0</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D45" s="13"/>
       <c r="E45" s="12" t="s">
@@ -8426,16 +8480,16 @@
     </row>
     <row r="46">
       <c r="A46" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B46" s="12">
         <v>6.0</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>14</v>
@@ -8446,13 +8500,13 @@
     </row>
     <row r="47">
       <c r="A47" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B47" s="12">
         <v>7.0</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D47" s="13"/>
       <c r="E47" s="12" t="s">
@@ -8464,16 +8518,16 @@
     </row>
     <row r="48">
       <c r="A48" s="12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B48" s="12">
         <v>7.0</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>14</v>
@@ -8484,13 +8538,13 @@
     </row>
     <row r="49">
       <c r="A49" s="12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B49" s="12">
         <v>7.0</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D49" s="13"/>
       <c r="E49" s="12" t="s">
@@ -8502,7 +8556,7 @@
     </row>
     <row r="50">
       <c r="A50" s="12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B50" s="12">
         <v>7.0</v>
@@ -8511,7 +8565,7 @@
         <v>48</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>14</v>
@@ -8522,16 +8576,16 @@
     </row>
     <row r="51">
       <c r="A51" s="12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B51" s="12">
         <v>7.0</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>14</v>
@@ -8542,13 +8596,13 @@
     </row>
     <row r="52">
       <c r="A52" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B52" s="12">
         <v>8.0</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D52" s="13"/>
       <c r="E52" s="12" t="s">
@@ -8560,16 +8614,16 @@
     </row>
     <row r="53">
       <c r="A53" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B53" s="12">
         <v>8.0</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>14</v>
@@ -8580,16 +8634,16 @@
     </row>
     <row r="54">
       <c r="A54" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B54" s="12">
         <v>8.0</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>14</v>
@@ -8600,16 +8654,16 @@
     </row>
     <row r="55">
       <c r="A55" s="12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B55" s="12">
         <v>8.0</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>14</v>
@@ -8620,13 +8674,13 @@
     </row>
     <row r="56">
       <c r="A56" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B56" s="12">
         <v>9.0</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D56" s="13"/>
       <c r="E56" s="12" t="s">
@@ -8638,16 +8692,16 @@
     </row>
     <row r="57">
       <c r="A57" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B57" s="12">
         <v>9.0</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>14</v>
@@ -8658,13 +8712,13 @@
     </row>
     <row r="58">
       <c r="A58" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B58" s="12">
         <v>9.0</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D58" s="13"/>
       <c r="E58" s="12" t="s">
@@ -8676,13 +8730,13 @@
     </row>
     <row r="59">
       <c r="A59" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B59" s="12">
         <v>9.0</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>17</v>
@@ -8696,16 +8750,16 @@
     </row>
     <row r="60">
       <c r="A60" s="12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B60" s="12">
         <v>9.0</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>14</v>
@@ -8716,16 +8770,16 @@
     </row>
     <row r="61">
       <c r="A61" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B61" s="12">
         <v>10.0</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E61" s="12" t="s">
         <v>14</v>
@@ -8736,16 +8790,16 @@
     </row>
     <row r="62">
       <c r="A62" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B62" s="12">
         <v>10.0</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>14</v>
@@ -8756,16 +8810,16 @@
     </row>
     <row r="63">
       <c r="A63" s="12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B63" s="12">
         <v>10.0</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E63" s="12" t="s">
         <v>14</v>
@@ -8776,16 +8830,16 @@
     </row>
     <row r="64">
       <c r="A64" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B64" s="12">
         <v>10.0</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>14</v>
@@ -8796,13 +8850,13 @@
     </row>
     <row r="65">
       <c r="A65" s="12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>154</v>
@@ -8816,7 +8870,7 @@
     </row>
     <row r="66">
       <c r="A66" s="12" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>148</v>
@@ -8824,9 +8878,7 @@
       <c r="C66" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D66" s="12" t="s">
-        <v>259</v>
-      </c>
+      <c r="D66" s="12"/>
       <c r="E66" s="12" t="s">
         <v>14</v>
       </c>
@@ -8836,7 +8888,7 @@
     </row>
     <row r="67">
       <c r="A67" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>148</v>
@@ -8844,9 +8896,7 @@
       <c r="C67" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D67" s="12" t="s">
-        <v>259</v>
-      </c>
+      <c r="D67" s="12"/>
       <c r="E67" s="12" t="s">
         <v>14</v>
       </c>
@@ -8856,7 +8906,7 @@
     </row>
     <row r="68">
       <c r="A68" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>148</v>
@@ -8864,9 +8914,7 @@
       <c r="C68" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D68" s="12" t="s">
-        <v>259</v>
-      </c>
+      <c r="D68" s="12"/>
       <c r="E68" s="12" t="s">
         <v>14</v>
       </c>
@@ -8876,21 +8924,119 @@
     </row>
     <row r="69">
       <c r="A69" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>259</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="D69" s="12"/>
       <c r="E69" s="12" t="s">
         <v>14</v>
       </c>
       <c r="F69" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" s="15" t="s">
         <v>15</v>
       </c>
     </row>
@@ -8925,7 +9071,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="17" t="s">
         <v>8</v>
@@ -8936,13 +9082,13 @@
     </row>
     <row r="2">
       <c r="A2" s="18" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B2" s="16">
         <v>1.0</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D2" s="18"/>
       <c r="E2" s="19" t="s">
@@ -8954,13 +9100,13 @@
     </row>
     <row r="3">
       <c r="A3" s="18" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B3" s="16">
         <v>1.0</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D3" s="18"/>
       <c r="E3" s="19" t="s">
@@ -8972,13 +9118,13 @@
     </row>
     <row r="4">
       <c r="A4" s="18" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B4" s="16">
         <v>1.0</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="19" t="s">
@@ -8990,13 +9136,13 @@
     </row>
     <row r="5">
       <c r="A5" s="18" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B5" s="16">
         <v>1.0</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="19" t="s">
@@ -9008,13 +9154,13 @@
     </row>
     <row r="6">
       <c r="A6" s="18" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B6" s="16">
         <v>1.0</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="19" t="s">
@@ -9026,13 +9172,13 @@
     </row>
     <row r="7">
       <c r="A7" s="18" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B7" s="16">
         <v>1.0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="19" t="s">
@@ -9044,13 +9190,13 @@
     </row>
     <row r="8">
       <c r="A8" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B8" s="16">
         <v>1.0</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="19" t="s">
@@ -9062,13 +9208,13 @@
     </row>
     <row r="9">
       <c r="A9" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B9" s="16">
         <v>1.0</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="19" t="s">
@@ -9080,16 +9226,16 @@
     </row>
     <row r="10">
       <c r="A10" s="18" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B10" s="16">
         <v>1.0</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>14</v>
@@ -9100,16 +9246,16 @@
     </row>
     <row r="11">
       <c r="A11" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B11" s="16">
         <v>1.0</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>14</v>
@@ -9120,13 +9266,13 @@
     </row>
     <row r="12">
       <c r="A12" s="18" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B12" s="16">
         <v>1.0</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="19" t="s">
@@ -9138,13 +9284,13 @@
     </row>
     <row r="13">
       <c r="A13" s="18" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B13" s="16">
         <v>2.0</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="19" t="s">
@@ -9156,13 +9302,13 @@
     </row>
     <row r="14">
       <c r="A14" s="18" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B14" s="16">
         <v>2.0</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="19" t="s">
@@ -9174,16 +9320,16 @@
     </row>
     <row r="15">
       <c r="A15" s="18" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B15" s="16">
         <v>2.0</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>14</v>
@@ -9194,16 +9340,16 @@
     </row>
     <row r="16">
       <c r="A16" s="18" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B16" s="16">
         <v>2.0</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>14</v>
@@ -9214,16 +9360,16 @@
     </row>
     <row r="17">
       <c r="A17" s="18" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B17" s="16">
         <v>2.0</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E17" s="19" t="s">
         <v>14</v>
@@ -9234,16 +9380,16 @@
     </row>
     <row r="18">
       <c r="A18" s="18" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B18" s="16">
         <v>2.0</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>14</v>
@@ -9254,7 +9400,7 @@
     </row>
     <row r="19">
       <c r="A19" s="18" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B19" s="16">
         <v>2.0</v>
@@ -9272,13 +9418,13 @@
     </row>
     <row r="20">
       <c r="A20" s="18" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B20" s="16">
         <v>2.0</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="19" t="s">
@@ -9290,13 +9436,13 @@
     </row>
     <row r="21">
       <c r="A21" s="18" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B21" s="16">
         <v>3.0</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="20" t="s">
@@ -9308,33 +9454,33 @@
     </row>
     <row r="22">
       <c r="A22" s="18" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B22" s="16">
         <v>3.0</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>59</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B23" s="16">
         <v>3.0</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="19" t="s">
@@ -9346,13 +9492,13 @@
     </row>
     <row r="24">
       <c r="A24" s="18" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B24" s="16">
         <v>3.0</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="19" t="s">
@@ -9364,31 +9510,31 @@
     </row>
     <row r="25">
       <c r="A25" s="18" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B25" s="16">
         <v>3.0</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D25" s="18"/>
       <c r="E25" s="20" t="s">
         <v>76</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B26" s="16">
         <v>3.0</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D26" s="18"/>
       <c r="E26" s="19" t="s">
@@ -9400,13 +9546,13 @@
     </row>
     <row r="27">
       <c r="A27" s="18" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B27" s="16">
         <v>3.0</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D27" s="18"/>
       <c r="E27" s="19" t="s">
@@ -9418,16 +9564,16 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B28" s="16">
         <v>3.0</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E28" s="20" t="s">
         <v>59</v>
@@ -9438,13 +9584,13 @@
     </row>
     <row r="29">
       <c r="A29" s="18" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B29" s="16">
         <v>4.0</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D29" s="18"/>
       <c r="E29" s="20" t="s">
@@ -9456,36 +9602,36 @@
     </row>
     <row r="30">
       <c r="A30" s="18" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B30" s="16">
         <v>4.0</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E30" s="20" t="s">
         <v>76</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B31" s="16">
         <v>4.0</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>14</v>
@@ -9496,16 +9642,16 @@
     </row>
     <row r="32">
       <c r="A32" s="18" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B32" s="16">
         <v>4.0</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E32" s="20" t="s">
         <v>76</v>
@@ -9516,13 +9662,13 @@
     </row>
     <row r="33">
       <c r="A33" s="18" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B33" s="16">
         <v>4.0</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D33" s="18"/>
       <c r="E33" s="19" t="s">
@@ -9534,31 +9680,31 @@
     </row>
     <row r="34">
       <c r="A34" s="18" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B34" s="16">
         <v>4.0</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D34" s="18"/>
       <c r="E34" s="20" t="s">
         <v>76</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B35" s="16">
         <v>5.0</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D35" s="18"/>
       <c r="E35" s="19" t="s">
@@ -9570,52 +9716,52 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B36" s="16">
         <v>5.0</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D36" s="18"/>
       <c r="E36" s="20" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B37" s="16">
         <v>5.0</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D37" s="18"/>
       <c r="E37" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B38" s="16">
         <v>5.0</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>14</v>
@@ -9626,16 +9772,16 @@
     </row>
     <row r="39">
       <c r="A39" s="18" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B39" s="16">
         <v>5.0</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>76</v>
@@ -9646,55 +9792,55 @@
     </row>
     <row r="40">
       <c r="A40" s="18" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B40" s="16">
         <v>5.0</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B41" s="16">
         <v>5.0</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D41" s="18"/>
       <c r="E41" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B42" s="16">
         <v>6.0</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D42" s="18"/>
       <c r="E42" s="20" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>15</v>
@@ -9702,16 +9848,16 @@
     </row>
     <row r="43">
       <c r="A43" s="18" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B43" s="16">
         <v>6.0</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E43" s="20" t="s">
         <v>59</v>
@@ -9722,36 +9868,36 @@
     </row>
     <row r="44">
       <c r="A44" s="18" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B44" s="16">
         <v>6.0</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="18" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B45" s="16">
         <v>6.0</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E45" s="20" t="s">
         <v>123</v>
@@ -9762,7 +9908,7 @@
     </row>
     <row r="46">
       <c r="A46" s="18" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B46" s="16">
         <v>6.0</v>
@@ -9780,13 +9926,13 @@
     </row>
     <row r="47">
       <c r="A47" s="18" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B47" s="16">
         <v>7.0</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D47" s="18"/>
       <c r="E47" s="19" t="s">
@@ -9798,13 +9944,13 @@
     </row>
     <row r="48">
       <c r="A48" s="18" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B48" s="16">
         <v>7.0</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D48" s="18"/>
       <c r="E48" s="20" t="s">
@@ -9816,17 +9962,17 @@
     </row>
     <row r="49">
       <c r="A49" s="18" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B49" s="16">
         <v>7.0</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="D49" s="18"/>
       <c r="E49" s="20" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>15</v>
@@ -9834,16 +9980,16 @@
     </row>
     <row r="50">
       <c r="A50" s="18" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B50" s="16">
         <v>7.0</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E50" s="20" t="s">
         <v>123</v>
@@ -9854,33 +10000,33 @@
     </row>
     <row r="51">
       <c r="A51" s="18" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B51" s="16">
         <v>7.0</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E51" s="20" t="s">
         <v>63</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="18" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B52" s="16">
         <v>7.0</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D52" s="18"/>
       <c r="E52" s="20" t="s">
@@ -9892,13 +10038,13 @@
     </row>
     <row r="53">
       <c r="A53" s="18" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D53" s="18"/>
       <c r="E53" s="19" t="s">
@@ -9910,13 +10056,13 @@
     </row>
     <row r="54">
       <c r="A54" s="18" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D54" s="18"/>
       <c r="E54" s="19" t="s">
@@ -9928,13 +10074,13 @@
     </row>
     <row r="55">
       <c r="A55" s="18" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D55" s="18"/>
       <c r="E55" s="19" t="s">
@@ -9946,13 +10092,13 @@
     </row>
     <row r="56">
       <c r="A56" s="18" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D56" s="18"/>
       <c r="E56" s="19" t="s">
@@ -9964,13 +10110,13 @@
     </row>
     <row r="57">
       <c r="A57" s="21" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>209</v>
+        <v>347</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>154</v>
@@ -9984,16 +10130,16 @@
     </row>
     <row r="58">
       <c r="A58" s="12" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>14</v>
@@ -10004,16 +10150,16 @@
     </row>
     <row r="59">
       <c r="A59" s="12" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E59" s="24" t="s">
         <v>14</v>
@@ -10024,16 +10170,16 @@
     </row>
     <row r="60">
       <c r="A60" s="12" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E60" s="24" t="s">
         <v>14</v>
@@ -10044,16 +10190,16 @@
     </row>
     <row r="61">
       <c r="A61" s="12" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E61" s="24" t="s">
         <v>14</v>
@@ -10063,7 +10209,24 @@
       </c>
     </row>
     <row r="62">
-      <c r="E62" s="14"/>
+      <c r="A62" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E62" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" s="25" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="63">
       <c r="E63" s="14"/>
@@ -12880,10 +13043,10 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
@@ -12894,14 +13057,14 @@
     </row>
     <row r="2">
       <c r="A2" s="26" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B2" s="27">
         <v>1.0</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="26" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="E2" s="26">
         <v>20.0</v>
@@ -12910,14 +13073,14 @@
     </row>
     <row r="3">
       <c r="A3" s="26" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="B3" s="27">
         <v>1.0</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="E3" s="26">
         <v>30.0</v>
@@ -12926,16 +13089,16 @@
     </row>
     <row r="4">
       <c r="A4" s="26" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B4" s="27">
         <v>1.0</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E4" s="27">
         <v>160.0</v>
@@ -12944,16 +13107,16 @@
     </row>
     <row r="5">
       <c r="A5" s="26" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B5" s="27">
         <v>1.0</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E5" s="27">
         <v>250.0</v>
@@ -12962,16 +13125,16 @@
     </row>
     <row r="6">
       <c r="A6" s="26" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="B6" s="27">
         <v>1.0</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E6" s="27">
         <v>180.0</v>
@@ -12980,16 +13143,16 @@
     </row>
     <row r="7">
       <c r="A7" s="26" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B7" s="27">
         <v>1.0</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E7" s="27">
         <v>170.0</v>
@@ -12998,16 +13161,16 @@
     </row>
     <row r="8">
       <c r="A8" s="26" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B8" s="27">
         <v>1.0</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E8" s="27">
         <v>270.0</v>
@@ -13016,16 +13179,16 @@
     </row>
     <row r="9">
       <c r="A9" s="26" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B9" s="27">
         <v>1.0</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E9" s="27">
         <v>270.0</v>
@@ -13034,16 +13197,16 @@
     </row>
     <row r="10">
       <c r="A10" s="26" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B10" s="27">
         <v>1.0</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E10" s="27">
         <v>1580.0</v>
@@ -13052,16 +13215,16 @@
     </row>
     <row r="11">
       <c r="A11" s="26" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B11" s="27">
         <v>1.0</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E11" s="27">
         <v>280.0</v>
@@ -13070,16 +13233,16 @@
     </row>
     <row r="12">
       <c r="A12" s="26" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B12" s="27">
         <v>1.0</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E12" s="27">
         <v>2020.0</v>
@@ -13088,16 +13251,16 @@
     </row>
     <row r="13">
       <c r="A13" s="26" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B13" s="27">
         <v>1.0</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="E13" s="27">
         <v>90.0</v>
@@ -13106,16 +13269,16 @@
     </row>
     <row r="14">
       <c r="A14" s="26" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B14" s="27">
         <v>1.0</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="E14" s="27">
         <v>310.0</v>
@@ -13124,16 +13287,16 @@
     </row>
     <row r="15">
       <c r="A15" s="26" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B15" s="27">
         <v>1.0</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="E15" s="27">
         <v>480.0</v>
@@ -13142,16 +13305,16 @@
     </row>
     <row r="16">
       <c r="A16" s="26" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B16" s="27">
         <v>1.0</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E16" s="27">
         <v>180.0</v>
@@ -13160,16 +13323,16 @@
     </row>
     <row r="17">
       <c r="A17" s="26" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B17" s="27">
         <v>1.0</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E17" s="27">
         <v>180.0</v>
@@ -13178,16 +13341,16 @@
     </row>
     <row r="18">
       <c r="A18" s="26" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B18" s="27">
         <v>1.0</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E18" s="27">
         <v>180.0</v>
@@ -13196,16 +13359,16 @@
     </row>
     <row r="19">
       <c r="A19" s="26" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B19" s="27">
         <v>1.0</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E19" s="27">
         <v>180.0</v>
@@ -13214,16 +13377,16 @@
     </row>
     <row r="20">
       <c r="A20" s="26" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="B20" s="27">
         <v>1.0</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E20" s="27">
         <v>180.0</v>
@@ -13232,36 +13395,36 @@
     </row>
     <row r="21">
       <c r="A21" s="26" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B21" s="27">
         <v>1.0</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E21" s="27">
         <v>500.0</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="26" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B22" s="27">
         <v>1.0</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E22" s="27">
         <v>500.0</v>
@@ -13270,16 +13433,16 @@
     </row>
     <row r="23">
       <c r="A23" s="26" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B23" s="27">
         <v>1.0</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E23" s="27">
         <v>500.0</v>
@@ -13288,16 +13451,16 @@
     </row>
     <row r="24">
       <c r="A24" s="26" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B24" s="27">
         <v>1.0</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E24" s="27">
         <v>500.0</v>
@@ -13306,16 +13469,16 @@
     </row>
     <row r="25">
       <c r="A25" s="26" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B25" s="27">
         <v>1.0</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="E25" s="27">
         <v>500.0</v>
@@ -13324,16 +13487,16 @@
     </row>
     <row r="26">
       <c r="A26" s="26" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B26" s="27">
         <v>1.0</v>
       </c>
       <c r="C26" s="26" t="s">
+        <v>411</v>
+      </c>
+      <c r="D26" s="26" t="s">
         <v>400</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>389</v>
       </c>
       <c r="E26" s="27">
         <v>830.0</v>
@@ -13342,176 +13505,176 @@
     </row>
     <row r="27">
       <c r="A27" s="26" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="B27" s="27">
         <v>1.0</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E27" s="27">
         <v>550.0</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="26" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="B28" s="27">
         <v>1.0</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E28" s="27">
         <v>670.0</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="26" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B29" s="27">
         <v>1.0</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E29" s="27">
         <v>670.0</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="26" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="B30" s="27">
         <v>1.0</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E30" s="27">
         <v>670.0</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="26" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B31" s="27">
         <v>1.0</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E31" s="27">
         <v>670.0</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="26" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B32" s="27">
         <v>1.0</v>
       </c>
       <c r="C32" s="26" t="s">
+        <v>425</v>
+      </c>
+      <c r="D32" s="26" t="s">
         <v>414</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>403</v>
       </c>
       <c r="E32" s="27">
         <v>570.0</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="26" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B33" s="27">
         <v>1.0</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E33" s="27">
         <v>570.0</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="26" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B34" s="27">
         <v>1.0</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E34" s="27">
         <v>570.0</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="26" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="B35" s="27">
         <v>2.0</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="E35" s="27">
         <v>290.0</v>
@@ -13520,16 +13683,16 @@
     </row>
     <row r="36">
       <c r="A36" s="26" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="B36" s="27">
         <v>2.0</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="E36" s="27">
         <v>300.0</v>
@@ -13538,36 +13701,36 @@
     </row>
     <row r="37">
       <c r="A37" s="26" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B37" s="27">
         <v>2.0</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="E37" s="27">
         <v>520.0</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="B38" s="27">
         <v>3.0</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="E38" s="27">
         <v>490.0</v>
@@ -13576,16 +13739,16 @@
     </row>
     <row r="39">
       <c r="A39" s="26" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B39" s="27">
         <v>3.0</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="E39" s="27">
         <v>640.0</v>
@@ -13594,16 +13757,16 @@
     </row>
     <row r="40">
       <c r="A40" s="26" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B40" s="27">
         <v>3.0</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="E40" s="27">
         <v>900.0</v>
@@ -13612,16 +13775,16 @@
     </row>
     <row r="41">
       <c r="A41" s="26" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="B41" s="27">
         <v>4.0</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E41" s="27">
         <v>780.0</v>
@@ -13630,16 +13793,16 @@
     </row>
     <row r="42">
       <c r="A42" s="26" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="B42" s="27">
         <v>4.0</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="E42" s="27">
         <v>670.0</v>
@@ -13648,16 +13811,16 @@
     </row>
     <row r="43">
       <c r="A43" s="26" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="B43" s="27">
         <v>5.0</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="E43" s="27">
         <v>730.0</v>
@@ -13666,16 +13829,16 @@
     </row>
     <row r="44">
       <c r="A44" s="26" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B44" s="27">
         <v>5.0</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="E44" s="27">
         <v>840.0</v>
@@ -13684,16 +13847,16 @@
     </row>
     <row r="45">
       <c r="A45" s="26" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="B45" s="27">
         <v>5.0</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="E45" s="27">
         <v>1340.0</v>
@@ -13702,16 +13865,16 @@
     </row>
     <row r="46">
       <c r="A46" s="26" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="B46" s="27">
         <v>6.0</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="E46" s="27">
         <v>410.0</v>
@@ -13720,16 +13883,16 @@
     </row>
     <row r="47">
       <c r="A47" s="26" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="B47" s="27">
         <v>6.0</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="E47" s="27">
         <v>530.0</v>
@@ -13738,16 +13901,16 @@
     </row>
     <row r="48">
       <c r="A48" s="26" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="B48" s="27">
         <v>7.0</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="E48" s="27">
         <v>2260.0</v>
@@ -13756,16 +13919,16 @@
     </row>
     <row r="49">
       <c r="A49" s="26" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="B49" s="27">
         <v>7.0</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="E49" s="27">
         <v>710.0</v>
@@ -13774,16 +13937,16 @@
     </row>
     <row r="50">
       <c r="A50" s="26" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="B50" s="27">
         <v>8.0</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E50" s="27">
         <v>850.0</v>
@@ -13792,36 +13955,36 @@
     </row>
     <row r="51">
       <c r="A51" s="26" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B51" s="27">
         <v>8.0</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="E51" s="27">
         <v>1310.0</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="26" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="B52" s="27">
         <v>8.0</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="E52" s="27">
         <v>1350.0</v>
@@ -13830,16 +13993,16 @@
     </row>
     <row r="53">
       <c r="A53" s="26" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B53" s="27">
         <v>9.0</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="E53" s="27">
         <v>1760.0</v>
@@ -13848,16 +14011,16 @@
     </row>
     <row r="54">
       <c r="A54" s="26" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="B54" s="27">
         <v>9.0</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="E54" s="27">
         <v>1230.0</v>
@@ -13866,16 +14029,16 @@
     </row>
     <row r="55">
       <c r="A55" s="29" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="B55" s="30">
         <v>10.0</v>
       </c>
       <c r="C55" s="29" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="E55" s="30">
         <v>1990.0</v>
@@ -13884,16 +14047,16 @@
     </row>
     <row r="56">
       <c r="A56" s="29" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B56" s="30">
         <v>10.0</v>
       </c>
       <c r="C56" s="29" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="E56" s="30">
         <v>2980.0</v>
@@ -13902,662 +14065,662 @@
     </row>
     <row r="57">
       <c r="A57" s="26" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="B57" s="27">
         <v>1.0</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="E57" s="27">
         <v>690.0</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="26" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B58" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="E58" s="27">
         <v>280.0</v>
       </c>
       <c r="F58" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="26" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B59" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="E59" s="27">
         <v>280.0</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="26" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B60" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="E60" s="27">
         <v>630.0</v>
       </c>
       <c r="F60" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="26" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B61" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="E61" s="27">
         <v>340.0</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="26" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B62" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="E62" s="27">
         <v>330.0</v>
       </c>
       <c r="F62" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="26" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B63" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="E63" s="27">
         <v>330.0</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="26" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B64" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="E64" s="27">
         <v>350.0</v>
       </c>
       <c r="F64" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="26" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B65" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="E65" s="27">
         <v>360.0</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="26" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B66" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="E66" s="27">
         <v>360.0</v>
       </c>
       <c r="F66" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="26" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B67" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="E67" s="27">
         <v>1630.0</v>
       </c>
       <c r="F67" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="26" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="B68" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="E68" s="27">
         <v>130.0</v>
       </c>
       <c r="F68" s="27" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="E69" s="12">
         <v>900.0</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C70" s="27" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="E70" s="12">
         <v>820.0</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C71" s="27" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="E71" s="12">
         <v>280.0</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C72" s="27" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="E72" s="12">
         <v>1230.0</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C73" s="27" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="E73" s="12">
         <v>1150.0</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C74" s="27" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="E74" s="12">
         <v>260.0</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C75" s="27" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="E75" s="12">
         <v>330.0</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C76" s="27" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="E76" s="12">
         <v>330.0</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C77" s="27" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="E77" s="12">
         <v>330.0</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C78" s="27" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="E78" s="12">
         <v>330.0</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C79" s="27" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="E79" s="12">
         <v>330.0</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C80" s="27" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E80" s="12">
         <v>460.0</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C81" s="27" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E81" s="12">
         <v>480.0</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C82" s="27" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E82" s="12">
         <v>480.0</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C83" s="27" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E83" s="12">
         <v>480.0</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C84" s="27" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E84" s="12">
         <v>480.0</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E85" s="12">
         <v>800.0</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C86" s="27" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E86" s="12">
         <v>910.0</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C87" s="27" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E87" s="12">
         <v>480.0</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C88" s="27" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="E88" s="12">
         <v>1960.0</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C89" s="27" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="E89" s="12">
         <v>2370.0</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/heartowiki.xlsx
+++ b/heartowiki.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="609">
   <si>
     <t>도감 버전</t>
   </si>
@@ -23,7 +23,7 @@
     <t>마지막 업데이트</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.0.3</t>
   </si>
   <si>
     <t>이름</t>
@@ -1077,6 +1077,63 @@
   </si>
   <si>
     <t>스크립터 벌 사건</t>
+  </si>
+  <si>
+    <t>이사벨라나방</t>
+  </si>
+  <si>
+    <t>혜성꼬리나방</t>
+  </si>
+  <si>
+    <t>도시근교</t>
+  </si>
+  <si>
+    <t>가로등</t>
+  </si>
+  <si>
+    <t>장수풍뎅이</t>
+  </si>
+  <si>
+    <t>어촌 동쪽부두</t>
+  </si>
+  <si>
+    <t>피카소노린재</t>
+  </si>
+  <si>
+    <t>보랏빛해변</t>
+  </si>
+  <si>
+    <t>화단</t>
+  </si>
+  <si>
+    <t>황금귀신사슴벌레</t>
+  </si>
+  <si>
+    <t>무지개사슴벌레</t>
+  </si>
+  <si>
+    <t>나무 기둥 (추가 사건에서만 등장)</t>
+  </si>
+  <si>
+    <t>악마꽃사마귀</t>
+  </si>
+  <si>
+    <t>진주네발나비</t>
+  </si>
+  <si>
+    <t>푸른목수벌</t>
+  </si>
+  <si>
+    <t>헬레나몰포나비</t>
+  </si>
+  <si>
+    <t>헤쿠바몰포나비</t>
+  </si>
+  <si>
+    <t>헤라클레스풍뎅이</t>
+  </si>
+  <si>
+    <t>나선주머니나방</t>
   </si>
   <si>
     <t>재료</t>
@@ -1579,6 +1636,64 @@
     <t>웨슬리와 울피 인연 소집령 6일차 출석 보상</t>
   </si>
   <si>
+    <t>온천란</t>
+  </si>
+  <si>
+    <t>멸균란 ×1</t>
+  </si>
+  <si>
+    <t>온천란 레시피</t>
+  </si>
+  <si>
+    <t>온천 지역에 전용 요리 오브젝트에서만 조리 가능.</t>
+  </si>
+  <si>
+    <t>부활절 달걀</t>
+  </si>
+  <si>
+    <t>달걀 ×1
+우유 ×1</t>
+  </si>
+  <si>
+    <t>부활절 달걀 레시피</t>
+  </si>
+  <si>
+    <t>부활의 노래 이벤트 한정 레시피</t>
+  </si>
+  <si>
+    <t>부활절 보라 달걀</t>
+  </si>
+  <si>
+    <t>달걀 ×1
+포도 ×1</t>
+  </si>
+  <si>
+    <t>부활절 초록 달걀</t>
+  </si>
+  <si>
+    <t>달걀 ×1
+양상추 ×1</t>
+  </si>
+  <si>
+    <t>부활절 주황 달걀</t>
+  </si>
+  <si>
+    <t>달걀 ×1
+사과 ×1</t>
+  </si>
+  <si>
+    <t>부활절 이스터에그 파티</t>
+  </si>
+  <si>
+    <t>부활절 달걀 ×1
+부활절 보라 달걀 ×1
+부활절 초록 달걀 ×1
+부활절 주황 달걀 ×1</t>
+  </si>
+  <si>
+    <t>부활절 이스터에그 파티 레시피</t>
+  </si>
+  <si>
     <t>얼음컵 커피</t>
   </si>
   <si>
@@ -1681,18 +1796,6 @@
   </si>
   <si>
     <t>오로라 만찬 레시피</t>
-  </si>
-  <si>
-    <t>온천란</t>
-  </si>
-  <si>
-    <t>멸균란 ×1</t>
-  </si>
-  <si>
-    <t>온천란 레시피</t>
-  </si>
-  <si>
-    <t>온천 지역에 전용 요리 오브젝트에서만 조리 가능.</t>
   </si>
   <si>
     <t>짭짤한 팝콘통</t>
@@ -1997,7 +2100,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2069,6 +2172,12 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -10229,43 +10338,243 @@
       </c>
     </row>
     <row r="63">
-      <c r="E63" s="14"/>
+      <c r="A63" s="26" t="s">
+        <v>354</v>
+      </c>
+      <c r="B63" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="C63" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="64">
-      <c r="E64" s="14"/>
+      <c r="A64" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="B64" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="D64" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="E64" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F64" s="26" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="65">
-      <c r="E65" s="14"/>
+      <c r="A65" s="26" t="s">
+        <v>358</v>
+      </c>
+      <c r="B65" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="C65" s="26" t="s">
+        <v>359</v>
+      </c>
+      <c r="D65" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="E65" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F65" s="26" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="66">
-      <c r="E66" s="14"/>
+      <c r="A66" s="26" t="s">
+        <v>360</v>
+      </c>
+      <c r="B66" s="26">
+        <v>8.0</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>361</v>
+      </c>
+      <c r="D66" s="26" t="s">
+        <v>362</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F66" s="26" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="67">
-      <c r="E67" s="14"/>
+      <c r="A67" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="B67" s="26">
+        <v>9.0</v>
+      </c>
+      <c r="C67" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="D67" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="E67" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F67" s="26" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="68">
-      <c r="E68" s="14"/>
+      <c r="A68" s="26" t="s">
+        <v>364</v>
+      </c>
+      <c r="B68" s="26">
+        <v>9.0</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>365</v>
+      </c>
+      <c r="E68" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" s="25" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="69">
-      <c r="E69" s="14"/>
+      <c r="A69" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="B69" s="26">
+        <v>9.0</v>
+      </c>
+      <c r="C69" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="E69" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F69" s="26" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="70">
-      <c r="E70" s="14"/>
+      <c r="A70" s="26" t="s">
+        <v>367</v>
+      </c>
+      <c r="B70" s="26">
+        <v>9.0</v>
+      </c>
+      <c r="C70" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="E70" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F70" s="26" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="71">
-      <c r="E71" s="14"/>
+      <c r="A71" s="26" t="s">
+        <v>368</v>
+      </c>
+      <c r="B71" s="26">
+        <v>9.0</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="E71" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F71" s="26" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="72">
-      <c r="E72" s="14"/>
+      <c r="A72" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="B72" s="26">
+        <v>10.0</v>
+      </c>
+      <c r="C72" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F72" s="26" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="73">
-      <c r="E73" s="14"/>
+      <c r="A73" s="26" t="s">
+        <v>370</v>
+      </c>
+      <c r="B73" s="26">
+        <v>10.0</v>
+      </c>
+      <c r="C73" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F73" s="26" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="74">
-      <c r="E74" s="14"/>
+      <c r="A74" s="26" t="s">
+        <v>371</v>
+      </c>
+      <c r="B74" s="26">
+        <v>10.0</v>
+      </c>
+      <c r="C74" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="E74" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F74" s="26" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="75">
-      <c r="E75" s="14"/>
+      <c r="A75" s="26" t="s">
+        <v>372</v>
+      </c>
+      <c r="B75" s="26">
+        <v>10.0</v>
+      </c>
+      <c r="C75" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E75" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F75" s="26" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="76">
       <c r="E76" s="14"/>
@@ -13031,7 +13340,7 @@
     <col customWidth="1" min="2" max="2" width="15.63"/>
     <col customWidth="1" min="3" max="3" width="20.13"/>
     <col customWidth="1" min="4" max="4" width="26.88"/>
-    <col customWidth="1" min="5" max="5" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="5.13"/>
     <col customWidth="1" min="6" max="6" width="62.88"/>
   </cols>
   <sheetData>
@@ -13043,10 +13352,10 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
@@ -13056,1671 +13365,1771 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="s">
-        <v>356</v>
-      </c>
-      <c r="B2" s="27">
+      <c r="A2" s="28" t="s">
+        <v>375</v>
+      </c>
+      <c r="B2" s="29">
         <v>1.0</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26" t="s">
-        <v>357</v>
-      </c>
-      <c r="E2" s="26">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2" s="28">
         <v>20.0</v>
       </c>
-      <c r="F2" s="26"/>
+      <c r="F2" s="28"/>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="s">
-        <v>358</v>
-      </c>
-      <c r="B3" s="27">
+      <c r="A3" s="28" t="s">
+        <v>377</v>
+      </c>
+      <c r="B3" s="29">
         <v>1.0</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26" t="s">
-        <v>357</v>
-      </c>
-      <c r="E3" s="26">
+      <c r="C3" s="28"/>
+      <c r="D3" s="28" t="s">
+        <v>376</v>
+      </c>
+      <c r="E3" s="28">
         <v>30.0</v>
       </c>
-      <c r="F3" s="26"/>
+      <c r="F3" s="28"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="s">
-        <v>359</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="B4" s="29">
         <v>1.0</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>360</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="E4" s="27">
+      <c r="C4" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E4" s="29">
         <v>160.0</v>
       </c>
-      <c r="F4" s="28"/>
+      <c r="F4" s="30"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="s">
-        <v>362</v>
-      </c>
-      <c r="B5" s="27">
+      <c r="A5" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="B5" s="29">
         <v>1.0</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>363</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="E5" s="27">
+      <c r="C5" s="28" t="s">
+        <v>382</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E5" s="29">
         <v>250.0</v>
       </c>
-      <c r="F5" s="28"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="B6" s="27">
+      <c r="A6" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="B6" s="29">
         <v>1.0</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>365</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="E6" s="27">
+      <c r="C6" s="28" t="s">
+        <v>384</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E6" s="29">
         <v>180.0</v>
       </c>
-      <c r="F6" s="26"/>
+      <c r="F6" s="28"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="s">
-        <v>366</v>
-      </c>
-      <c r="B7" s="27">
+      <c r="A7" s="28" t="s">
+        <v>385</v>
+      </c>
+      <c r="B7" s="29">
         <v>1.0</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>367</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="E7" s="27">
+      <c r="C7" s="28" t="s">
+        <v>386</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E7" s="29">
         <v>170.0</v>
       </c>
-      <c r="F7" s="28"/>
+      <c r="F7" s="30"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="s">
-        <v>368</v>
-      </c>
-      <c r="B8" s="27">
+      <c r="A8" s="28" t="s">
+        <v>387</v>
+      </c>
+      <c r="B8" s="29">
         <v>1.0</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>369</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="E8" s="27">
+      <c r="C8" s="28" t="s">
+        <v>388</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E8" s="29">
         <v>270.0</v>
       </c>
-      <c r="F8" s="28"/>
+      <c r="F8" s="30"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="s">
-        <v>370</v>
-      </c>
-      <c r="B9" s="27">
+      <c r="A9" s="28" t="s">
+        <v>389</v>
+      </c>
+      <c r="B9" s="29">
         <v>1.0</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="E9" s="27">
+      <c r="C9" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E9" s="29">
         <v>270.0</v>
       </c>
-      <c r="F9" s="28"/>
+      <c r="F9" s="30"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="s">
-        <v>372</v>
-      </c>
-      <c r="B10" s="27">
+      <c r="A10" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="B10" s="29">
         <v>1.0</v>
       </c>
-      <c r="C10" s="26" t="s">
-        <v>373</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="E10" s="27">
+      <c r="C10" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E10" s="29">
         <v>1580.0</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="28"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="s">
-        <v>374</v>
-      </c>
-      <c r="B11" s="27">
+      <c r="A11" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="B11" s="29">
         <v>1.0</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>375</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="E11" s="27">
+      <c r="C11" s="28" t="s">
+        <v>394</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E11" s="29">
         <v>280.0</v>
       </c>
-      <c r="F11" s="28"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="s">
-        <v>376</v>
-      </c>
-      <c r="B12" s="27">
+      <c r="A12" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="B12" s="29">
         <v>1.0</v>
       </c>
-      <c r="C12" s="26" t="s">
-        <v>377</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="E12" s="27">
+      <c r="C12" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E12" s="29">
         <v>2020.0</v>
       </c>
-      <c r="F12" s="26"/>
+      <c r="F12" s="28"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="s">
-        <v>378</v>
-      </c>
-      <c r="B13" s="27">
+      <c r="A13" s="28" t="s">
+        <v>397</v>
+      </c>
+      <c r="B13" s="29">
         <v>1.0</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>380</v>
-      </c>
-      <c r="E13" s="27">
+      <c r="C13" s="28" t="s">
+        <v>398</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>399</v>
+      </c>
+      <c r="E13" s="29">
         <v>90.0</v>
       </c>
-      <c r="F13" s="26"/>
+      <c r="F13" s="28"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="s">
-        <v>381</v>
-      </c>
-      <c r="B14" s="27">
+      <c r="A14" s="28" t="s">
+        <v>400</v>
+      </c>
+      <c r="B14" s="29">
         <v>1.0</v>
       </c>
-      <c r="C14" s="26" t="s">
-        <v>382</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>383</v>
-      </c>
-      <c r="E14" s="27">
+      <c r="C14" s="28" t="s">
+        <v>401</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>402</v>
+      </c>
+      <c r="E14" s="29">
         <v>310.0</v>
       </c>
-      <c r="F14" s="28"/>
+      <c r="F14" s="30"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="s">
-        <v>384</v>
-      </c>
-      <c r="B15" s="27">
+      <c r="A15" s="28" t="s">
+        <v>403</v>
+      </c>
+      <c r="B15" s="29">
         <v>1.0</v>
       </c>
-      <c r="C15" s="26" t="s">
-        <v>385</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>386</v>
-      </c>
-      <c r="E15" s="27">
+      <c r="C15" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>405</v>
+      </c>
+      <c r="E15" s="29">
         <v>480.0</v>
       </c>
-      <c r="F15" s="28"/>
+      <c r="F15" s="30"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="s">
-        <v>387</v>
-      </c>
-      <c r="B16" s="27">
+      <c r="A16" s="28" t="s">
+        <v>406</v>
+      </c>
+      <c r="B16" s="29">
         <v>1.0</v>
       </c>
-      <c r="C16" s="26" t="s">
-        <v>388</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>389</v>
-      </c>
-      <c r="E16" s="27">
+      <c r="C16" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="E16" s="29">
         <v>180.0</v>
       </c>
-      <c r="F16" s="26"/>
+      <c r="F16" s="28"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="s">
-        <v>390</v>
-      </c>
-      <c r="B17" s="27">
+      <c r="A17" s="28" t="s">
+        <v>409</v>
+      </c>
+      <c r="B17" s="29">
         <v>1.0</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>391</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>389</v>
-      </c>
-      <c r="E17" s="27">
+      <c r="C17" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="E17" s="29">
         <v>180.0</v>
       </c>
-      <c r="F17" s="28"/>
+      <c r="F17" s="30"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="B18" s="27">
+      <c r="A18" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="B18" s="29">
         <v>1.0</v>
       </c>
-      <c r="C18" s="26" t="s">
-        <v>393</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>389</v>
-      </c>
-      <c r="E18" s="27">
+      <c r="C18" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="E18" s="29">
         <v>180.0</v>
       </c>
-      <c r="F18" s="28"/>
+      <c r="F18" s="30"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="s">
-        <v>394</v>
-      </c>
-      <c r="B19" s="27">
+      <c r="A19" s="28" t="s">
+        <v>413</v>
+      </c>
+      <c r="B19" s="29">
         <v>1.0</v>
       </c>
-      <c r="C19" s="26" t="s">
-        <v>395</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>389</v>
-      </c>
-      <c r="E19" s="27">
+      <c r="C19" s="28" t="s">
+        <v>414</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="E19" s="29">
         <v>180.0</v>
       </c>
-      <c r="F19" s="28"/>
+      <c r="F19" s="30"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="s">
-        <v>396</v>
-      </c>
-      <c r="B20" s="27">
+      <c r="A20" s="28" t="s">
+        <v>415</v>
+      </c>
+      <c r="B20" s="29">
         <v>1.0</v>
       </c>
-      <c r="C20" s="26" t="s">
-        <v>397</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>389</v>
-      </c>
-      <c r="E20" s="27">
+      <c r="C20" s="28" t="s">
+        <v>416</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="E20" s="29">
         <v>180.0</v>
       </c>
-      <c r="F20" s="28"/>
+      <c r="F20" s="30"/>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="s">
-        <v>398</v>
-      </c>
-      <c r="B21" s="27">
+      <c r="A21" s="28" t="s">
+        <v>417</v>
+      </c>
+      <c r="B21" s="29">
         <v>1.0</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>399</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>400</v>
-      </c>
-      <c r="E21" s="27">
+      <c r="C21" s="28" t="s">
+        <v>418</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="E21" s="29">
         <v>500.0</v>
       </c>
-      <c r="F21" s="27" t="s">
-        <v>401</v>
+      <c r="F21" s="29" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="s">
-        <v>402</v>
-      </c>
-      <c r="B22" s="27">
+      <c r="A22" s="28" t="s">
+        <v>421</v>
+      </c>
+      <c r="B22" s="29">
         <v>1.0</v>
       </c>
-      <c r="C22" s="26" t="s">
-        <v>403</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>400</v>
-      </c>
-      <c r="E22" s="27">
+      <c r="C22" s="28" t="s">
+        <v>422</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="E22" s="29">
         <v>500.0</v>
       </c>
-      <c r="F22" s="28"/>
+      <c r="F22" s="30"/>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="s">
-        <v>404</v>
-      </c>
-      <c r="B23" s="27">
+      <c r="A23" s="28" t="s">
+        <v>423</v>
+      </c>
+      <c r="B23" s="29">
         <v>1.0</v>
       </c>
-      <c r="C23" s="26" t="s">
-        <v>405</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>400</v>
-      </c>
-      <c r="E23" s="27">
+      <c r="C23" s="28" t="s">
+        <v>424</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="E23" s="29">
         <v>500.0</v>
       </c>
-      <c r="F23" s="28"/>
+      <c r="F23" s="30"/>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="s">
-        <v>406</v>
-      </c>
-      <c r="B24" s="27">
+      <c r="A24" s="28" t="s">
+        <v>425</v>
+      </c>
+      <c r="B24" s="29">
         <v>1.0</v>
       </c>
-      <c r="C24" s="26" t="s">
-        <v>407</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>400</v>
-      </c>
-      <c r="E24" s="27">
+      <c r="C24" s="28" t="s">
+        <v>426</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="E24" s="29">
         <v>500.0</v>
       </c>
-      <c r="F24" s="28"/>
+      <c r="F24" s="30"/>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="s">
-        <v>408</v>
-      </c>
-      <c r="B25" s="27">
+      <c r="A25" s="28" t="s">
+        <v>427</v>
+      </c>
+      <c r="B25" s="29">
         <v>1.0</v>
       </c>
-      <c r="C25" s="26" t="s">
-        <v>409</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>400</v>
-      </c>
-      <c r="E25" s="27">
+      <c r="C25" s="28" t="s">
+        <v>428</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="E25" s="29">
         <v>500.0</v>
       </c>
-      <c r="F25" s="28"/>
+      <c r="F25" s="30"/>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="s">
-        <v>410</v>
-      </c>
-      <c r="B26" s="27">
+      <c r="A26" s="28" t="s">
+        <v>429</v>
+      </c>
+      <c r="B26" s="29">
         <v>1.0</v>
       </c>
-      <c r="C26" s="26" t="s">
-        <v>411</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>400</v>
-      </c>
-      <c r="E26" s="27">
+      <c r="C26" s="28" t="s">
+        <v>430</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="E26" s="29">
         <v>830.0</v>
       </c>
-      <c r="F26" s="26"/>
+      <c r="F26" s="28"/>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="s">
-        <v>412</v>
-      </c>
-      <c r="B27" s="27">
+      <c r="A27" s="28" t="s">
+        <v>431</v>
+      </c>
+      <c r="B27" s="29">
         <v>1.0</v>
       </c>
-      <c r="C27" s="26" t="s">
-        <v>413</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="E27" s="27">
+      <c r="C27" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="E27" s="29">
         <v>550.0</v>
       </c>
-      <c r="F27" s="27" t="s">
-        <v>415</v>
+      <c r="F27" s="29" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="s">
-        <v>416</v>
-      </c>
-      <c r="B28" s="27">
+      <c r="A28" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="B28" s="29">
         <v>1.0</v>
       </c>
-      <c r="C28" s="26" t="s">
-        <v>417</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="E28" s="27">
+      <c r="C28" s="28" t="s">
+        <v>436</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="E28" s="29">
         <v>670.0</v>
       </c>
-      <c r="F28" s="27" t="s">
-        <v>415</v>
+      <c r="F28" s="29" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="s">
-        <v>418</v>
-      </c>
-      <c r="B29" s="27">
+      <c r="A29" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="B29" s="29">
         <v>1.0</v>
       </c>
-      <c r="C29" s="26" t="s">
-        <v>419</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="E29" s="27">
+      <c r="C29" s="28" t="s">
+        <v>438</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="E29" s="29">
         <v>670.0</v>
       </c>
-      <c r="F29" s="27" t="s">
-        <v>415</v>
+      <c r="F29" s="29" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="s">
-        <v>420</v>
-      </c>
-      <c r="B30" s="27">
+      <c r="A30" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="B30" s="29">
         <v>1.0</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>421</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="E30" s="27">
+      <c r="C30" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="E30" s="29">
         <v>670.0</v>
       </c>
-      <c r="F30" s="27" t="s">
-        <v>415</v>
+      <c r="F30" s="29" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="B31" s="27">
+      <c r="A31" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="B31" s="29">
         <v>1.0</v>
       </c>
-      <c r="C31" s="27" t="s">
-        <v>423</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="E31" s="27">
+      <c r="C31" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="E31" s="29">
         <v>670.0</v>
       </c>
-      <c r="F31" s="27" t="s">
-        <v>415</v>
+      <c r="F31" s="29" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="s">
-        <v>424</v>
-      </c>
-      <c r="B32" s="27">
+      <c r="A32" s="28" t="s">
+        <v>443</v>
+      </c>
+      <c r="B32" s="29">
         <v>1.0</v>
       </c>
-      <c r="C32" s="26" t="s">
-        <v>425</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="E32" s="27">
+      <c r="C32" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="E32" s="29">
         <v>570.0</v>
       </c>
-      <c r="F32" s="27" t="s">
-        <v>415</v>
+      <c r="F32" s="29" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26" t="s">
-        <v>426</v>
-      </c>
-      <c r="B33" s="27">
+      <c r="A33" s="28" t="s">
+        <v>445</v>
+      </c>
+      <c r="B33" s="29">
         <v>1.0</v>
       </c>
-      <c r="C33" s="26" t="s">
-        <v>427</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="E33" s="27">
+      <c r="C33" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="E33" s="29">
         <v>570.0</v>
       </c>
-      <c r="F33" s="27" t="s">
-        <v>415</v>
+      <c r="F33" s="29" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="s">
-        <v>428</v>
-      </c>
-      <c r="B34" s="27">
+      <c r="A34" s="28" t="s">
+        <v>447</v>
+      </c>
+      <c r="B34" s="29">
         <v>1.0</v>
       </c>
-      <c r="C34" s="26" t="s">
-        <v>429</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>414</v>
-      </c>
-      <c r="E34" s="27">
+      <c r="C34" s="28" t="s">
+        <v>448</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>433</v>
+      </c>
+      <c r="E34" s="29">
         <v>570.0</v>
       </c>
-      <c r="F34" s="27" t="s">
-        <v>415</v>
+      <c r="F34" s="29" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="s">
-        <v>430</v>
-      </c>
-      <c r="B35" s="27">
+      <c r="A35" s="28" t="s">
+        <v>449</v>
+      </c>
+      <c r="B35" s="29">
         <v>2.0</v>
       </c>
-      <c r="C35" s="26" t="s">
-        <v>431</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>432</v>
-      </c>
-      <c r="E35" s="27">
+      <c r="C35" s="28" t="s">
+        <v>450</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="E35" s="29">
         <v>290.0</v>
       </c>
-      <c r="F35" s="28"/>
+      <c r="F35" s="30"/>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="B36" s="27">
+      <c r="A36" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="B36" s="29">
         <v>2.0</v>
       </c>
-      <c r="C36" s="26" t="s">
-        <v>434</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>432</v>
-      </c>
-      <c r="E36" s="27">
+      <c r="C36" s="28" t="s">
+        <v>453</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="E36" s="29">
         <v>300.0</v>
       </c>
-      <c r="F36" s="26"/>
+      <c r="F36" s="28"/>
     </row>
     <row r="37">
-      <c r="A37" s="26" t="s">
-        <v>435</v>
-      </c>
-      <c r="B37" s="27">
+      <c r="A37" s="28" t="s">
+        <v>454</v>
+      </c>
+      <c r="B37" s="29">
         <v>2.0</v>
       </c>
-      <c r="C37" s="26" t="s">
-        <v>436</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>437</v>
-      </c>
-      <c r="E37" s="27">
+      <c r="C37" s="28" t="s">
+        <v>455</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>456</v>
+      </c>
+      <c r="E37" s="29">
         <v>520.0</v>
       </c>
-      <c r="F37" s="27" t="s">
-        <v>438</v>
+      <c r="F37" s="29" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="s">
-        <v>439</v>
-      </c>
-      <c r="B38" s="27">
+      <c r="A38" s="28" t="s">
+        <v>458</v>
+      </c>
+      <c r="B38" s="29">
         <v>3.0</v>
       </c>
-      <c r="C38" s="26" t="s">
-        <v>440</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>439</v>
-      </c>
-      <c r="E38" s="27">
+      <c r="C38" s="28" t="s">
+        <v>459</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>458</v>
+      </c>
+      <c r="E38" s="29">
         <v>490.0</v>
       </c>
-      <c r="F38" s="28"/>
+      <c r="F38" s="30"/>
     </row>
     <row r="39">
-      <c r="A39" s="26" t="s">
-        <v>441</v>
-      </c>
-      <c r="B39" s="27">
+      <c r="A39" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="B39" s="29">
         <v>3.0</v>
       </c>
-      <c r="C39" s="26" t="s">
-        <v>442</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>441</v>
-      </c>
-      <c r="E39" s="27">
+      <c r="C39" s="28" t="s">
+        <v>461</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="E39" s="29">
         <v>640.0</v>
       </c>
-      <c r="F39" s="28"/>
+      <c r="F39" s="30"/>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="s">
-        <v>443</v>
-      </c>
-      <c r="B40" s="27">
+      <c r="A40" s="28" t="s">
+        <v>462</v>
+      </c>
+      <c r="B40" s="29">
         <v>3.0</v>
       </c>
-      <c r="C40" s="26" t="s">
-        <v>444</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>443</v>
-      </c>
-      <c r="E40" s="27">
+      <c r="C40" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>462</v>
+      </c>
+      <c r="E40" s="29">
         <v>900.0</v>
       </c>
-      <c r="F40" s="26"/>
+      <c r="F40" s="28"/>
     </row>
     <row r="41">
-      <c r="A41" s="26" t="s">
-        <v>445</v>
-      </c>
-      <c r="B41" s="27">
+      <c r="A41" s="28" t="s">
+        <v>464</v>
+      </c>
+      <c r="B41" s="29">
         <v>4.0</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>446</v>
-      </c>
-      <c r="D41" s="26" t="s">
-        <v>447</v>
-      </c>
-      <c r="E41" s="27">
+      <c r="C41" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>466</v>
+      </c>
+      <c r="E41" s="29">
         <v>780.0</v>
       </c>
-      <c r="F41" s="28"/>
+      <c r="F41" s="30"/>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="s">
-        <v>448</v>
-      </c>
-      <c r="B42" s="27">
+      <c r="A42" s="28" t="s">
+        <v>467</v>
+      </c>
+      <c r="B42" s="29">
         <v>4.0</v>
       </c>
-      <c r="C42" s="26" t="s">
-        <v>449</v>
-      </c>
-      <c r="D42" s="26" t="s">
-        <v>450</v>
-      </c>
-      <c r="E42" s="27">
+      <c r="C42" s="28" t="s">
+        <v>468</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>469</v>
+      </c>
+      <c r="E42" s="29">
         <v>670.0</v>
       </c>
-      <c r="F42" s="28"/>
+      <c r="F42" s="30"/>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="s">
-        <v>451</v>
-      </c>
-      <c r="B43" s="27">
+      <c r="A43" s="28" t="s">
+        <v>470</v>
+      </c>
+      <c r="B43" s="29">
         <v>5.0</v>
       </c>
-      <c r="C43" s="26" t="s">
-        <v>452</v>
-      </c>
-      <c r="D43" s="26" t="s">
-        <v>453</v>
-      </c>
-      <c r="E43" s="27">
+      <c r="C43" s="28" t="s">
+        <v>471</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>472</v>
+      </c>
+      <c r="E43" s="29">
         <v>730.0</v>
       </c>
-      <c r="F43" s="28"/>
+      <c r="F43" s="30"/>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="s">
-        <v>454</v>
-      </c>
-      <c r="B44" s="27">
+      <c r="A44" s="28" t="s">
+        <v>473</v>
+      </c>
+      <c r="B44" s="29">
         <v>5.0</v>
       </c>
-      <c r="C44" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="D44" s="26" t="s">
-        <v>456</v>
-      </c>
-      <c r="E44" s="27">
+      <c r="C44" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>475</v>
+      </c>
+      <c r="E44" s="29">
         <v>840.0</v>
       </c>
-      <c r="F44" s="28"/>
+      <c r="F44" s="30"/>
     </row>
     <row r="45">
-      <c r="A45" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="B45" s="27">
+      <c r="A45" s="28" t="s">
+        <v>476</v>
+      </c>
+      <c r="B45" s="29">
         <v>5.0</v>
       </c>
-      <c r="C45" s="26" t="s">
-        <v>458</v>
-      </c>
-      <c r="D45" s="26" t="s">
-        <v>459</v>
-      </c>
-      <c r="E45" s="27">
+      <c r="C45" s="28" t="s">
+        <v>477</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>478</v>
+      </c>
+      <c r="E45" s="29">
         <v>1340.0</v>
       </c>
-      <c r="F45" s="28"/>
+      <c r="F45" s="30"/>
     </row>
     <row r="46">
-      <c r="A46" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="B46" s="27">
+      <c r="A46" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="B46" s="29">
         <v>6.0</v>
       </c>
-      <c r="C46" s="26" t="s">
-        <v>461</v>
-      </c>
-      <c r="D46" s="26" t="s">
-        <v>462</v>
-      </c>
-      <c r="E46" s="27">
+      <c r="C46" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="E46" s="29">
         <v>410.0</v>
       </c>
-      <c r="F46" s="28"/>
+      <c r="F46" s="30"/>
     </row>
     <row r="47">
-      <c r="A47" s="26" t="s">
-        <v>463</v>
-      </c>
-      <c r="B47" s="27">
+      <c r="A47" s="28" t="s">
+        <v>482</v>
+      </c>
+      <c r="B47" s="29">
         <v>6.0</v>
       </c>
-      <c r="C47" s="26" t="s">
-        <v>464</v>
-      </c>
-      <c r="D47" s="26" t="s">
-        <v>465</v>
-      </c>
-      <c r="E47" s="27">
+      <c r="C47" s="28" t="s">
+        <v>483</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="E47" s="29">
         <v>530.0</v>
       </c>
-      <c r="F47" s="26"/>
+      <c r="F47" s="28"/>
     </row>
     <row r="48">
-      <c r="A48" s="26" t="s">
-        <v>466</v>
-      </c>
-      <c r="B48" s="27">
+      <c r="A48" s="28" t="s">
+        <v>485</v>
+      </c>
+      <c r="B48" s="29">
         <v>7.0</v>
       </c>
-      <c r="C48" s="26" t="s">
-        <v>467</v>
-      </c>
-      <c r="D48" s="26" t="s">
-        <v>468</v>
-      </c>
-      <c r="E48" s="27">
+      <c r="C48" s="28" t="s">
+        <v>486</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>487</v>
+      </c>
+      <c r="E48" s="29">
         <v>2260.0</v>
       </c>
-      <c r="F48" s="26"/>
+      <c r="F48" s="28"/>
     </row>
     <row r="49">
-      <c r="A49" s="26" t="s">
-        <v>469</v>
-      </c>
-      <c r="B49" s="27">
+      <c r="A49" s="28" t="s">
+        <v>488</v>
+      </c>
+      <c r="B49" s="29">
         <v>7.0</v>
       </c>
-      <c r="C49" s="26" t="s">
-        <v>470</v>
-      </c>
-      <c r="D49" s="26" t="s">
-        <v>471</v>
-      </c>
-      <c r="E49" s="27">
+      <c r="C49" s="28" t="s">
+        <v>489</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="E49" s="29">
         <v>710.0</v>
       </c>
-      <c r="F49" s="26"/>
+      <c r="F49" s="28"/>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="s">
-        <v>472</v>
-      </c>
-      <c r="B50" s="27">
+      <c r="A50" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="B50" s="29">
         <v>8.0</v>
       </c>
-      <c r="C50" s="26" t="s">
-        <v>473</v>
-      </c>
-      <c r="D50" s="26" t="s">
-        <v>474</v>
-      </c>
-      <c r="E50" s="27">
+      <c r="C50" s="28" t="s">
+        <v>492</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>493</v>
+      </c>
+      <c r="E50" s="29">
         <v>850.0</v>
       </c>
-      <c r="F50" s="28"/>
+      <c r="F50" s="30"/>
     </row>
     <row r="51">
-      <c r="A51" s="26" t="s">
-        <v>475</v>
-      </c>
-      <c r="B51" s="27">
+      <c r="A51" s="28" t="s">
+        <v>494</v>
+      </c>
+      <c r="B51" s="29">
         <v>8.0</v>
       </c>
-      <c r="C51" s="26" t="s">
-        <v>476</v>
-      </c>
-      <c r="D51" s="26" t="s">
-        <v>474</v>
-      </c>
-      <c r="E51" s="27">
+      <c r="C51" s="28" t="s">
+        <v>495</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>493</v>
+      </c>
+      <c r="E51" s="29">
         <v>1310.0</v>
       </c>
-      <c r="F51" s="27" t="s">
-        <v>477</v>
+      <c r="F51" s="29" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="s">
-        <v>478</v>
-      </c>
-      <c r="B52" s="27">
+      <c r="A52" s="28" t="s">
+        <v>497</v>
+      </c>
+      <c r="B52" s="29">
         <v>8.0</v>
       </c>
-      <c r="C52" s="26" t="s">
-        <v>479</v>
-      </c>
-      <c r="D52" s="26" t="s">
-        <v>480</v>
-      </c>
-      <c r="E52" s="27">
+      <c r="C52" s="28" t="s">
+        <v>498</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>499</v>
+      </c>
+      <c r="E52" s="29">
         <v>1350.0</v>
       </c>
-      <c r="F52" s="26"/>
+      <c r="F52" s="28"/>
     </row>
     <row r="53">
-      <c r="A53" s="26" t="s">
-        <v>481</v>
-      </c>
-      <c r="B53" s="27">
+      <c r="A53" s="28" t="s">
+        <v>500</v>
+      </c>
+      <c r="B53" s="29">
         <v>9.0</v>
       </c>
-      <c r="C53" s="26" t="s">
-        <v>482</v>
-      </c>
-      <c r="D53" s="26" t="s">
-        <v>483</v>
-      </c>
-      <c r="E53" s="27">
+      <c r="C53" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="E53" s="29">
         <v>1760.0</v>
       </c>
-      <c r="F53" s="28"/>
+      <c r="F53" s="30"/>
     </row>
     <row r="54">
-      <c r="A54" s="26" t="s">
-        <v>484</v>
-      </c>
-      <c r="B54" s="27">
+      <c r="A54" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="B54" s="29">
         <v>9.0</v>
       </c>
-      <c r="C54" s="26" t="s">
-        <v>485</v>
-      </c>
-      <c r="D54" s="26" t="s">
-        <v>486</v>
-      </c>
-      <c r="E54" s="27">
+      <c r="C54" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="E54" s="29">
         <v>1230.0</v>
       </c>
-      <c r="F54" s="28"/>
+      <c r="F54" s="30"/>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="s">
-        <v>487</v>
-      </c>
-      <c r="B55" s="30">
+      <c r="A55" s="31" t="s">
+        <v>506</v>
+      </c>
+      <c r="B55" s="32">
         <v>10.0</v>
       </c>
-      <c r="C55" s="29" t="s">
-        <v>488</v>
-      </c>
-      <c r="D55" s="30" t="s">
-        <v>489</v>
-      </c>
-      <c r="E55" s="30">
+      <c r="C55" s="31" t="s">
+        <v>507</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>508</v>
+      </c>
+      <c r="E55" s="32">
         <v>1990.0</v>
       </c>
-      <c r="F55" s="31"/>
+      <c r="F55" s="33"/>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="s">
-        <v>490</v>
-      </c>
-      <c r="B56" s="30">
+      <c r="A56" s="31" t="s">
+        <v>509</v>
+      </c>
+      <c r="B56" s="32">
         <v>10.0</v>
       </c>
-      <c r="C56" s="29" t="s">
-        <v>488</v>
-      </c>
-      <c r="D56" s="29" t="s">
-        <v>489</v>
-      </c>
-      <c r="E56" s="30">
+      <c r="C56" s="31" t="s">
+        <v>507</v>
+      </c>
+      <c r="D56" s="31" t="s">
+        <v>508</v>
+      </c>
+      <c r="E56" s="32">
         <v>2980.0</v>
       </c>
-      <c r="F56" s="31"/>
+      <c r="F56" s="33"/>
     </row>
     <row r="57">
-      <c r="A57" s="26" t="s">
-        <v>491</v>
-      </c>
-      <c r="B57" s="27">
+      <c r="A57" s="28" t="s">
+        <v>510</v>
+      </c>
+      <c r="B57" s="29">
         <v>1.0</v>
       </c>
-      <c r="C57" s="27" t="s">
-        <v>492</v>
-      </c>
-      <c r="D57" s="26" t="s">
-        <v>493</v>
-      </c>
-      <c r="E57" s="27">
+      <c r="C57" s="29" t="s">
+        <v>511</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="E57" s="29">
         <v>690.0</v>
       </c>
-      <c r="F57" s="27" t="s">
-        <v>494</v>
+      <c r="F57" s="29" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="26" t="s">
-        <v>495</v>
-      </c>
-      <c r="B58" s="27" t="s">
+      <c r="A58" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="B58" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="E58" s="29">
+        <v>130.0</v>
+      </c>
+      <c r="F58" s="29" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="B59" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="C59" s="29" t="s">
+        <v>519</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>520</v>
+      </c>
+      <c r="E59" s="29">
+        <v>190.0</v>
+      </c>
+      <c r="F59" s="29" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="s">
+        <v>522</v>
+      </c>
+      <c r="B60" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="C60" s="29" t="s">
+        <v>523</v>
+      </c>
+      <c r="D60" s="29" t="s">
+        <v>520</v>
+      </c>
+      <c r="E60" s="29">
+        <v>620.0</v>
+      </c>
+      <c r="F60" s="29" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="s">
+        <v>524</v>
+      </c>
+      <c r="B61" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="C61" s="29" t="s">
+        <v>525</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>520</v>
+      </c>
+      <c r="E61" s="29">
+        <v>570.0</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="s">
+        <v>526</v>
+      </c>
+      <c r="B62" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="C62" s="29" t="s">
+        <v>527</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>520</v>
+      </c>
+      <c r="E62" s="29">
+        <v>190.0</v>
+      </c>
+      <c r="F62" s="29" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="s">
+        <v>528</v>
+      </c>
+      <c r="B63" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="C63" s="29" t="s">
+        <v>529</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>530</v>
+      </c>
+      <c r="E63" s="29">
+        <v>1650.0</v>
+      </c>
+      <c r="F63" s="29" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="28" t="s">
+        <v>531</v>
+      </c>
+      <c r="B64" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C58" s="26" t="s">
-        <v>496</v>
-      </c>
-      <c r="D58" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="E58" s="27">
+      <c r="C64" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>533</v>
+      </c>
+      <c r="E64" s="29">
         <v>280.0</v>
       </c>
-      <c r="F58" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="26" t="s">
-        <v>499</v>
-      </c>
-      <c r="B59" s="27" t="s">
+      <c r="F64" s="29" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="28" t="s">
+        <v>535</v>
+      </c>
+      <c r="B65" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C59" s="26" t="s">
-        <v>500</v>
-      </c>
-      <c r="D59" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="E59" s="27">
+      <c r="C65" s="28" t="s">
+        <v>536</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>533</v>
+      </c>
+      <c r="E65" s="29">
         <v>280.0</v>
       </c>
-      <c r="F59" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="26" t="s">
-        <v>501</v>
-      </c>
-      <c r="B60" s="27" t="s">
+      <c r="F65" s="29" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="s">
+        <v>537</v>
+      </c>
+      <c r="B66" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C60" s="26" t="s">
-        <v>502</v>
-      </c>
-      <c r="D60" s="26" t="s">
-        <v>503</v>
-      </c>
-      <c r="E60" s="27">
+      <c r="C66" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="D66" s="28" t="s">
+        <v>539</v>
+      </c>
+      <c r="E66" s="29">
         <v>630.0</v>
       </c>
-      <c r="F60" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="26" t="s">
-        <v>504</v>
-      </c>
-      <c r="B61" s="27" t="s">
+      <c r="F66" s="29" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="s">
+        <v>540</v>
+      </c>
+      <c r="B67" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C61" s="26" t="s">
-        <v>505</v>
-      </c>
-      <c r="D61" s="26" t="s">
-        <v>506</v>
-      </c>
-      <c r="E61" s="27">
+      <c r="C67" s="28" t="s">
+        <v>541</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>542</v>
+      </c>
+      <c r="E67" s="29">
         <v>340.0</v>
       </c>
-      <c r="F61" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="26" t="s">
-        <v>507</v>
-      </c>
-      <c r="B62" s="27" t="s">
+      <c r="F67" s="29" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="28" t="s">
+        <v>543</v>
+      </c>
+      <c r="B68" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C62" s="26" t="s">
-        <v>508</v>
-      </c>
-      <c r="D62" s="26" t="s">
-        <v>509</v>
-      </c>
-      <c r="E62" s="27">
+      <c r="C68" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="D68" s="28" t="s">
+        <v>545</v>
+      </c>
+      <c r="E68" s="29">
         <v>330.0</v>
       </c>
-      <c r="F62" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="26" t="s">
-        <v>510</v>
-      </c>
-      <c r="B63" s="27" t="s">
+      <c r="F68" s="29" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="28" t="s">
+        <v>546</v>
+      </c>
+      <c r="B69" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C63" s="26" t="s">
-        <v>511</v>
-      </c>
-      <c r="D63" s="26" t="s">
-        <v>509</v>
-      </c>
-      <c r="E63" s="27">
+      <c r="C69" s="28" t="s">
+        <v>547</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>545</v>
+      </c>
+      <c r="E69" s="29">
         <v>330.0</v>
       </c>
-      <c r="F63" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="26" t="s">
-        <v>512</v>
-      </c>
-      <c r="B64" s="27" t="s">
+      <c r="F69" s="29" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="s">
+        <v>548</v>
+      </c>
+      <c r="B70" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C64" s="26" t="s">
-        <v>513</v>
-      </c>
-      <c r="D64" s="26" t="s">
-        <v>509</v>
-      </c>
-      <c r="E64" s="27">
+      <c r="C70" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="D70" s="28" t="s">
+        <v>545</v>
+      </c>
+      <c r="E70" s="29">
         <v>350.0</v>
       </c>
-      <c r="F64" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="26" t="s">
-        <v>514</v>
-      </c>
-      <c r="B65" s="27" t="s">
+      <c r="F70" s="29" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="B71" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C65" s="26" t="s">
-        <v>515</v>
-      </c>
-      <c r="D65" s="26" t="s">
-        <v>509</v>
-      </c>
-      <c r="E65" s="27">
+      <c r="C71" s="28" t="s">
+        <v>551</v>
+      </c>
+      <c r="D71" s="28" t="s">
+        <v>545</v>
+      </c>
+      <c r="E71" s="29">
         <v>360.0</v>
       </c>
-      <c r="F65" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="26" t="s">
-        <v>516</v>
-      </c>
-      <c r="B66" s="27" t="s">
+      <c r="F71" s="29" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="B72" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C66" s="26" t="s">
-        <v>517</v>
-      </c>
-      <c r="D66" s="26" t="s">
-        <v>509</v>
-      </c>
-      <c r="E66" s="27">
+      <c r="C72" s="28" t="s">
+        <v>553</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>545</v>
+      </c>
+      <c r="E72" s="29">
         <v>360.0</v>
       </c>
-      <c r="F66" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="26" t="s">
-        <v>518</v>
-      </c>
-      <c r="B67" s="27" t="s">
+      <c r="F72" s="29" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28" t="s">
+        <v>554</v>
+      </c>
+      <c r="B73" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="C67" s="27" t="s">
-        <v>519</v>
-      </c>
-      <c r="D67" s="26" t="s">
-        <v>520</v>
-      </c>
-      <c r="E67" s="27">
+      <c r="C73" s="29" t="s">
+        <v>555</v>
+      </c>
+      <c r="D73" s="28" t="s">
+        <v>556</v>
+      </c>
+      <c r="E73" s="29">
         <v>1630.0</v>
       </c>
-      <c r="F67" s="27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="26" t="s">
-        <v>521</v>
-      </c>
-      <c r="B68" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>522</v>
-      </c>
-      <c r="D68" s="26" t="s">
-        <v>523</v>
-      </c>
-      <c r="E68" s="27">
-        <v>130.0</v>
-      </c>
-      <c r="F68" s="27" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C69" s="27" t="s">
-        <v>526</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="E69" s="12">
-        <v>900.0</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="s">
-        <v>529</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C70" s="27" t="s">
-        <v>530</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>531</v>
-      </c>
-      <c r="E70" s="12">
-        <v>820.0</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="s">
-        <v>532</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C71" s="27" t="s">
-        <v>533</v>
-      </c>
-      <c r="D71" s="12" t="s">
+      <c r="F73" s="29" t="s">
         <v>534</v>
-      </c>
-      <c r="E71" s="12">
-        <v>280.0</v>
-      </c>
-      <c r="F71" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="s">
-        <v>535</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C72" s="27" t="s">
-        <v>536</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>537</v>
-      </c>
-      <c r="E72" s="12">
-        <v>1230.0</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C73" s="27" t="s">
-        <v>539</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="E73" s="12">
-        <v>1150.0</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C74" s="27" t="s">
-        <v>542</v>
+      <c r="C74" s="29" t="s">
+        <v>558</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="E74" s="12">
-        <v>260.0</v>
+        <v>900.0</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="27" t="s">
-        <v>545</v>
+      <c r="C75" s="29" t="s">
+        <v>562</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="E75" s="12">
-        <v>330.0</v>
+        <v>820.0</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C76" s="27" t="s">
-        <v>548</v>
+      <c r="C76" s="29" t="s">
+        <v>565</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="E76" s="12">
-        <v>330.0</v>
+        <v>280.0</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C77" s="27" t="s">
-        <v>550</v>
+      <c r="C77" s="29" t="s">
+        <v>568</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="E77" s="12">
-        <v>330.0</v>
+        <v>1230.0</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="s">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C78" s="27" t="s">
-        <v>552</v>
+      <c r="C78" s="29" t="s">
+        <v>571</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>546</v>
+        <v>572</v>
       </c>
       <c r="E78" s="12">
-        <v>330.0</v>
+        <v>1150.0</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C79" s="27" t="s">
-        <v>554</v>
+      <c r="C79" s="29" t="s">
+        <v>574</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>546</v>
+        <v>575</v>
       </c>
       <c r="E79" s="12">
-        <v>330.0</v>
+        <v>260.0</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C80" s="27" t="s">
-        <v>556</v>
+      <c r="C80" s="29" t="s">
+        <v>577</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="E80" s="12">
-        <v>460.0</v>
+        <v>330.0</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C81" s="27" t="s">
-        <v>559</v>
+      <c r="C81" s="29" t="s">
+        <v>580</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="E81" s="12">
-        <v>480.0</v>
+        <v>330.0</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C82" s="27" t="s">
-        <v>561</v>
+      <c r="C82" s="29" t="s">
+        <v>582</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="E82" s="12">
-        <v>480.0</v>
+        <v>330.0</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C83" s="27" t="s">
-        <v>563</v>
+      <c r="C83" s="29" t="s">
+        <v>584</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="E83" s="12">
-        <v>480.0</v>
+        <v>330.0</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C84" s="27" t="s">
-        <v>565</v>
+      <c r="C84" s="29" t="s">
+        <v>586</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="E84" s="12">
-        <v>480.0</v>
+        <v>330.0</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C85" s="27" t="s">
-        <v>567</v>
+      <c r="C85" s="29" t="s">
+        <v>588</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="E85" s="12">
-        <v>800.0</v>
+        <v>460.0</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="s">
-        <v>568</v>
+        <v>590</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C86" s="27" t="s">
-        <v>569</v>
+      <c r="C86" s="29" t="s">
+        <v>591</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="E86" s="12">
-        <v>910.0</v>
+        <v>480.0</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="s">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C87" s="27" t="s">
-        <v>571</v>
+      <c r="C87" s="29" t="s">
+        <v>593</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="E87" s="12">
         <v>480.0</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="s">
-        <v>572</v>
+        <v>594</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C88" s="27" t="s">
-        <v>573</v>
+      <c r="C88" s="29" t="s">
+        <v>595</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="E88" s="12">
-        <v>1960.0</v>
+        <v>480.0</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="s">
-        <v>574</v>
+        <v>596</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C89" s="27" t="s">
-        <v>575</v>
+      <c r="C89" s="29" t="s">
+        <v>597</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="E89" s="12">
+        <v>480.0</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C90" s="29" t="s">
+        <v>599</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="E90" s="12">
+        <v>800.0</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C91" s="29" t="s">
+        <v>601</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="E91" s="12">
+        <v>910.0</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C92" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="E92" s="12">
+        <v>480.0</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C93" s="29" t="s">
+        <v>605</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="E93" s="12">
+        <v>1960.0</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C94" s="29" t="s">
+        <v>607</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="E94" s="12">
         <v>2370.0</v>
       </c>
-      <c r="F89" s="12" t="s">
-        <v>528</v>
+      <c r="F94" s="12" t="s">
+        <v>560</v>
       </c>
     </row>
   </sheetData>
